--- a/assets/part4/FAIR.xlsx
+++ b/assets/part4/FAIR.xlsx
@@ -282,7 +282,7 @@
     <t xml:space="preserve">C</t>
   </si>
   <si>
-    <t xml:space="preserve">1/4-20 UNC-2B (Go/No-Go)</t>
+    <t xml:space="preserve">1/4-20 UNC-2B</t>
   </si>
   <si>
     <t xml:space="preserve">PASS - Go/No-Go Thread Gauge</t>
@@ -716,347 +716,347 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
